--- a/data_qr/2026-05-20.xlsx
+++ b/data_qr/2026-05-20.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Desktop\my_first_website\data_qr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Desktop\my_first_website\data_QR\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
   <si>
     <t>EthSwitch S.C.</t>
   </si>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>Total</t>
-  </si>
-  <si>
-    <t>BANK</t>
   </si>
 </sst>
 </file>
@@ -679,9 +676,7 @@
       <c r="F4" s="16"/>
     </row>
     <row r="5" spans="2:6" ht="14.45" customHeight="1">
-      <c r="B5" s="17" t="s">
-        <v>36</v>
-      </c>
+      <c r="B5" s="17"/>
       <c r="C5" s="17" t="s">
         <v>3</v>
       </c>
